--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>44858</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45197</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44635</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>46049</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44475</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44475</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45733</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46195</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>44770</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44460</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45375</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45980</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45932</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>46013</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46195</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44648</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44882</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>44808</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44876</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44460</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>45629</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>44493</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45986</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44493</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>46069</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45428</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44475</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44592</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44949</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44959</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45366</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44650</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45713</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>45974</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>46049</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44493</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45035</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45068</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44698</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>46113</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44984</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44981</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44686</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44475</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45607</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45838</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44578</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>46037</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44483</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44599</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44804</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44799</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>44593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44536</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44468</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44650</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44498</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44474</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44474</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>44662</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44516</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44482</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44566</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>44599</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>44839</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>44650</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44498</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44853</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44882</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44882</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44740</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44594</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44687</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>44867</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44711</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44501</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44537</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44533</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44533</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44701</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44652</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44550</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44825</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44483</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>44613</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>44531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44574</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>44593</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44623</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44482</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44475</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44754</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44547</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44788</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44882</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44763</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45039</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44959</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45393</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45007</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45387</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45551</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45095</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45093</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45307</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45617</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44552</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45698</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>45698</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45071</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45260</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45487</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45110</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45281</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45457</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45093</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45371</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45371</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45376</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45238</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45320</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45243</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45177</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44902</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44985</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45629</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45704</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>45187</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45168</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45112</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>45698</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45095</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44566</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45253</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>44888</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45559</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45711</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44654</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45408</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45432</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44855</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45386</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44952</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45005</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44896</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44484</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45665</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45582</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45582</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45260</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45635</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45049</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45520</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45629</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45114</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45615</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45622</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44805</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45302</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44984</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45751</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44945</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44904</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45160</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45877</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45308</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45260</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45799</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45792</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44994</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>44600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45824</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45299</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45196</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>44816</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45798</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45524</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>44937</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45322</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45817</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45203</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45880</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45187</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45877</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45877</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>46066</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>46091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45908</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45700</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45911</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45729</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45796</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44503</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45688</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44876</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>44607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44634</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44519</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44589</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45196</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45243</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>44664</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45201</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45299</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45925</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45925</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45149</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44938</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46142</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44459</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45623</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45715</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45937</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45141</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>46146</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>46146</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>46105</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45098</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45520</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45520</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45944</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45261</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45944</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45945</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45729</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45099</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45020</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45222</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45106</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44686</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45964</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45103</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45288</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45641</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44533</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45978</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45320</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45971</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>44666</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46154</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45615</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45175</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45382</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45972</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44459</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45061</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45092</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>46154</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45978</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45600</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45980</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44544</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45755</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45761</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44629</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44985</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45986</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45946</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45111</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44913</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44672</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45217</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44573</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45861</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45617</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45995</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45382</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45635</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45630</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46003</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46003</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>46002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45279</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45646</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44727</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45096</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45575</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>46009</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44735</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46020</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46010</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44873</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46170</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>46030</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>46031</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45219</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45273</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46034</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45041</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44594</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45474</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45581</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45767</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45068</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44461</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46044</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44578</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46174</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46049</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45581</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45120</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46175</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46049</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>46051</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46178</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>46178</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45154</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45288</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44979</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>45175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>44952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>46069</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45546</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>46066</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45252</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>46066</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>46181</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>44593</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44945</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46181</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46181</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44491</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45035</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45723</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46181</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45260</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45218</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>44595</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46082</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44649</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45196</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46086</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45630</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45707</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>46190</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45450</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>46092</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46190</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>46092</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46190</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>46094</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>46094</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45370</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45258</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46100</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>46099</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>46099</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45366</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46100</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>44566</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>46104</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45099</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45168</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44846</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46107</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>44708</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46107</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44986</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45565</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45012</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46114</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45222</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44530</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45163</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>44715</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45163</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>46125</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45544</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>44902</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46203</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45184</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45618</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46132</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>46132</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45260</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45908</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45070</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44999</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46204</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45204</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45187</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45049</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45836</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45601</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45028</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45751</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45051</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45390</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>45390</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45688</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45803</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>44634</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45524</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>46205</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45636</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45693</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45308</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45629</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>44896</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45641</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45107</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45261</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45300</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44593</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45131</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45258</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45645</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>46254</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>46254</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>45175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44893</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>46258</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>46258</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>45118</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>44746</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>45299</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>44818</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>46220</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>46220</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>46222</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>46222</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>46222</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>46222</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>46222</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>46222</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>45386</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45306</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45775</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>46220</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>46220</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>46220</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>46220</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45174</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45736</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45229</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45411</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>46029</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45713</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45379</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45616</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>45782</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>45782</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>46272</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>46270</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46270</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>45784</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45784</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>45784</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>45911</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45784</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45784</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45789</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45553</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>46281</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45466</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45356</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44812</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45621</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45642</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>45044</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45630</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45800</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>44888</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45405</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45810</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45720</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45560</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45813</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45813</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45813</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45813</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45616</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45819</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45533</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45822</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45833</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45834</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45838</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45838</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45560</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45785</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45881</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45880</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45266</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45337</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>44834</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>44606</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45266</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45481</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45335</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44901</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45476</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44733</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>44763</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45076</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44596</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>44735</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45716</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>45964</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>46036</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44858</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45197</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44475</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44475</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45375</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45932</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45014</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44648</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44808</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>46069</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45929</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44493</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44475</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45035</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45607</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>46049</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>46093</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44686</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45838</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45366</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44949</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44650</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44493</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44959</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44984</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44805</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44593</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44536</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44468</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44650</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44474</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44474</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44662</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44566</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44599</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44498</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44882</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44882</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44740</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44544</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44594</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44687</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44656</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44867</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44712</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44488</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44711</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44533</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44701</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44652</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44550</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44531</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44613</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44574</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44593</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44482</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44475</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44754</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44483</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44547</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44788</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44872</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44882</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44622</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44763</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45281</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45272</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45177</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45370</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45203</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45546</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44816</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45243</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45382</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45386</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45229</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45387</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45408</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>44945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45390</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45260</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45260</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45258</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45035</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44984</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45520</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45450</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44973</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45621</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45299</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44846</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45817</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45792</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45751</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45635</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44595</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44896</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>46044</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45800</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45582</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45582</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46049</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>46051</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45908</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45551</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45204</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44552</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46066</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46066</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45379</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44887</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45925</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45320</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46082</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44629</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>45560</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45405</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44672</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46086</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45810</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45002</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44888</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44634</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>46092</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45937</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46094</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46094</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45238</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45944</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45945</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>46100</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44979</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46100</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45049</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46104</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45095</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45723</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45630</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44666</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46107</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45068</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45005</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46114</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45623</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46125</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45813</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45813</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45813</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45012</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46132</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45616</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45533</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45096</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46132</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45601</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45061</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44999</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44937</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45646</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45946</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45041</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45629</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45635</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45615</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45824</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45877</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45736</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45904</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45995</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45688</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45751</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45187</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45799</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45707</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45796</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45679</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45880</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46066</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44519</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45819</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45822</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45711</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45039</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44518</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45775</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45698</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45698</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45308</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45700</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45877</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44566</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45836</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45729</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44578</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44852</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>46105</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46146</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45721</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>44873</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45028</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46154</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45834</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45095</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46154</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44896</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45838</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44855</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45761</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45838</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45937</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45382</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45715</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45861</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44952</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45260</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45560</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45118</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>46170</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44902</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45279</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46175</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45020</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45112</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44525</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45615</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45565</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45457</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46178</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46181</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46181</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46178</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46181</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45617</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44503</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45411</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44986</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45163</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44589</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45616</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45629</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46190</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>46190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45785</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>46190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46190</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45729</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45630</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45880</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45881</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44566</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45600</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45217</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45636</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46203</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>44727</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44686</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45672</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45371</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45371</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>46205</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45175</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45201</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44594</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44818</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44607</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45077</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>44600</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44593</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44634</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45222</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>46254</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45111</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>46254</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45376</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45099</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45260</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45698</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44888</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>45261</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44664</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45175</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45688</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>46222</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>46222</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45093</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>44715</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>44735</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45322</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45288</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45713</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46222</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>46220</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>46220</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46220</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>46220</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>46222</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46222</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>46220</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45218</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>44754</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>46222</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46029</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45320</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45163</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45299</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45258</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46272</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>46270</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>46270</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>44938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44888</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45302</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44994</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45487</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45693</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45911</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45520</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46281</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>44904</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45581</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>44876</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45175</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45559</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>44491</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45622</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44945</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>44593</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45062</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45583</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44654</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>44484</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44895</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44533</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44746</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45051</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45307</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45260</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>44913</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45520</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45149</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45474</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45114</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44573</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45196</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44530</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44708</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>44893</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>44547</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45641</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45243</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45201</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45299</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45131</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45524</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45007</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45390</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44952</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44995</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>45049</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45160</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45617</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45366</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45103</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45196</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45629</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45141</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45141</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45411</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45665</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>44805</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45704</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45106</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45222</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45187</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45386</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45575</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45641</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45581</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45098</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>45107</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45734</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45645</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45767</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45432</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45300</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45782</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45782</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45784</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45784</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45784</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45784</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45784</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45553</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45466</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45789</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45356</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44812</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>44606</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>44733</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>44596</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44735</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>45266</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45337</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>44834</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45266</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45481</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45335</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>44901</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45476</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>44763</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45716</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45964</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46036</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45175</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44858</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45197</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44475</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44475</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45375</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45932</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45014</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44648</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44808</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>46069</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45929</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>45986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44493</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44475</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45035</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45607</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>46049</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>46093</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45940</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44686</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45838</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>45366</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44949</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44650</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44493</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44959</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44984</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44805</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44593</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44536</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44468</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44650</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44474</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44474</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44662</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44566</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44599</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44650</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44498</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44882</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44882</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44740</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44544</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44594</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44687</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44656</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44867</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44712</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44488</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44711</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44501</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44537</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44533</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44701</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44652</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44550</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44531</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44613</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44574</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44593</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44482</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44475</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44754</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44483</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44547</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44788</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44872</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44882</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44622</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44763</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45281</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45272</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45177</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45370</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45203</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45546</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44816</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45243</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45382</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45386</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45229</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45387</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45408</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>44945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45390</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45260</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45260</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45258</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45035</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44984</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45520</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45450</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44973</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45621</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45299</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44846</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45642</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>46031</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45817</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45792</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45751</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45635</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44595</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44896</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>46044</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45800</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45582</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45582</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46049</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>46051</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45908</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45551</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45204</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44552</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46066</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46066</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45379</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44887</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45925</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45320</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46082</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44629</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>45560</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45405</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44672</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46086</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45936</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45810</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45002</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44888</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44634</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>46092</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45937</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46094</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46094</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46099</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45238</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45944</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45945</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>46100</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44979</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46100</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45049</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46104</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45095</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45723</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45630</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44666</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46107</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45068</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45005</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46114</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45623</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46125</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45972</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45813</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45813</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45813</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45012</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46132</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45616</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45533</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45096</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46132</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45601</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45061</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44999</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44937</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45646</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45986</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45946</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45041</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45629</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45803</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45635</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45615</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45824</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45877</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45736</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45904</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45995</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45688</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45174</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45751</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45187</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45799</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45707</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45796</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45679</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45880</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>46066</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44519</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45819</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45822</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45711</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45039</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44518</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45775</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45698</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45698</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45308</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45700</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45877</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44566</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45836</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45729</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45177</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44578</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44852</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>46105</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46146</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45721</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>44873</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45028</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46154</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45833</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45834</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45095</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46154</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44896</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45838</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44855</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45761</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45838</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45937</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45382</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45715</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45861</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44952</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45260</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45560</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45118</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>46170</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44902</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45279</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46175</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45020</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45112</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44525</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45615</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45565</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45457</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46178</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46181</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46181</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46178</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>46181</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45617</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44503</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>45411</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44986</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45163</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>44589</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45616</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45629</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46190</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>46190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45785</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>46190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46190</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45729</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45630</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45880</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45881</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44566</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45600</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45217</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45636</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46203</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>44727</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44686</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45672</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45371</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45371</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>46205</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45175</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45201</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44594</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44818</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44607</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45077</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>44600</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44593</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44634</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45222</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>46254</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45111</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>46254</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45376</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45099</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45260</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45698</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44888</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>45261</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44664</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45175</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45688</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>46222</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>46222</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45093</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>44715</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>44735</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45322</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45288</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45713</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46222</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>46220</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>46220</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46220</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>46220</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>46222</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46222</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>46220</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45218</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>44754</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>46222</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46029</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45320</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45163</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45299</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45258</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46272</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>46270</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>46270</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>44938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44888</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45302</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44994</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45487</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45693</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45911</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45520</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46281</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>44904</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45581</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>44876</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45175</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45559</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>44491</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45622</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44945</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>44593</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45062</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45583</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44654</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>44484</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44895</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44533</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44746</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45051</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45307</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45260</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>44913</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45520</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45149</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45474</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45114</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44573</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45196</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44530</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>44708</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>44893</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>44547</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45641</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45243</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45201</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45299</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45131</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45524</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45007</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45390</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44952</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44995</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>45049</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45160</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45617</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45366</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45103</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45196</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45629</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45141</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45141</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45411</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45665</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>44805</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45704</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45106</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45222</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45187</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45386</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45575</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45641</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45581</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45098</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>45107</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45734</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45645</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45767</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45432</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45300</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45782</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45782</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45784</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45784</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45784</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45784</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45784</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45553</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45466</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45789</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45356</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44812</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>44606</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>44733</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>44596</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44735</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>45266</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45337</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>44834</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45266</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45481</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45335</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>44901</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45476</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>44763</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45716</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45964</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46036</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44858</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45197</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44475</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44475</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44770</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45375</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45980</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45014</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44648</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44808</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45929</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45986</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>44493</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44493</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46049</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44592</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45940</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>46093</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44949</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>45366</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44650</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>45713</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44493</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45035</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45068</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44593</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44536</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44498</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44474</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44474</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44662</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44566</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44599</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44650</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44498</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44853</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44882</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44594</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44656</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44867</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44712</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44488</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44711</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44501</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44537</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44533</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44701</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44652</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44483</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44613</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44531</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44574</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44593</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44623</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44482</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44475</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44483</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44547</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44754</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44788</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44872</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44622</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44763</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45039</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44959</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45387</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45095</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45617</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45007</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45307</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44552</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45201</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45071</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45260</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45487</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45077</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45583</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45457</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44902</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45376</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45320</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>46003</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>46003</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45371</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45466</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45356</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45243</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>46009</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45792</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46010</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>46030</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>46031</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45704</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45877</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45908</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45168</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45911</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46049</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45044</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45630</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44754</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45800</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45925</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45698</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45095</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44566</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45405</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46066</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44888</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45936</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45559</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>46066</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44654</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45944</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45810</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44888</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45944</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45945</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45002</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45408</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45560</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45432</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>44855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45813</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45813</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45411</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45386</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44852</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>46086</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45813</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45813</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45005</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46092</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46094</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44484</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45665</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45635</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46099</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45972</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44984</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46100</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45260</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45049</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45616</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>46104</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45533</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45629</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45622</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>46107</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45114</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45302</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45615</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46114</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44805</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45822</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>44945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46125</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45160</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45995</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>44525</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45260</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>46132</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>44600</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45833</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45299</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45838</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45187</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45838</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45836</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45751</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45524</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45322</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45803</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45877</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45560</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45308</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45729</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44503</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44876</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45799</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>44607</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44634</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44519</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44589</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45196</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45243</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44664</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45260</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45201</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45299</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45880</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45149</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>44896</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45904</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45877</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46066</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46091</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45700</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45623</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45715</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45141</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45796</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45688</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45520</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45520</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45729</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45734</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45020</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>46142</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45222</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>46146</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46146</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46105</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45106</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>44686</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>45103</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46154</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45641</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44533</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45320</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45148</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45785</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44666</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45615</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45382</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45937</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45061</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44547</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45092</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45861</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44544</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45755</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45761</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44629</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44985</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45880</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45880</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>46170</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>46170</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>45111</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44913</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44672</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45217</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44573</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>46178</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>46181</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>46181</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45382</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45635</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45721</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45630</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>46190</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>46190</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46190</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>44727</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45096</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45575</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44735</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44873</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46205</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45636</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45219</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44887</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45041</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>44594</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45581</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45767</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45068</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44518</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44578</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46258</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45120</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44995</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46220</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>46220</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>46222</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46222</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>46222</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>46222</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>46222</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46222</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45154</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46220</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46220</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>46220</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46220</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44979</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45175</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44952</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>46029</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45546</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45252</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>44593</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>44945</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>44491</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45723</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45218</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>44595</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>46270</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46270</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44649</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45911</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46281</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45707</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45450</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45370</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45366</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>44566</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45099</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44846</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>44708</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44986</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45565</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45012</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45222</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>44530</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>44715</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45163</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45544</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>44902</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45184</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45618</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45260</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45204</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45601</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>45028</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45051</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45390</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>45390</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45688</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45258</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44634</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45524</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46254</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45693</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>46296</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>46296</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>46254</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45308</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45629</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44896</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45641</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45107</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>45261</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45300</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44593</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45131</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45645</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>44893</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45118</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>44746</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45299</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>44818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45386</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45306</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>45775</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45736</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45229</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45411</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45713</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45616</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45782</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45784</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45784</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45784</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45784</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45784</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45789</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45553</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45337</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44834</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44606</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45266</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45481</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45335</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>44901</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45476</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>44733</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>44763</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>44596</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44735</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45716</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45964</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46036</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44858</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45197</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>46163</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44475</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44475</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44770</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45375</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45980</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45932</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45014</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44648</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>44882</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44808</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45929</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45986</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>44493</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44493</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44581</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46049</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>44592</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45940</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>46093</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44949</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>45366</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44650</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>45713</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44493</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45035</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45068</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44578</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44599</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44799</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44593</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44536</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44498</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44474</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44474</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44662</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44566</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44599</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44650</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44498</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44853</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44882</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44594</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44656</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44867</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44712</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44488</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44711</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44501</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44537</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44533</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44701</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44652</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44483</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44613</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44531</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44574</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44593</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44623</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44482</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44475</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44483</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44547</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44754</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44788</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44872</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44622</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44763</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45039</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44959</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45387</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45095</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45617</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45007</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45307</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44552</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45201</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45071</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45260</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45487</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45077</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45583</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45457</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44902</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45376</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45320</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45817</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>46003</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>46003</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45371</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45466</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45751</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45356</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45243</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>46009</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45792</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46010</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>46030</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>46031</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45704</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45877</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45908</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45168</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45911</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46049</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45044</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45917</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45630</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44754</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45800</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45925</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45698</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45095</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44566</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45405</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45711</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46066</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44888</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45936</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45559</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>46066</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44654</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45944</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45810</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44888</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45944</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45945</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45002</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45408</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45560</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45432</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>44855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45813</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45813</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45411</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45386</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44852</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>46086</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45813</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45813</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45005</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46092</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46094</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44484</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45665</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45635</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45112</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46099</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45972</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44984</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46100</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45260</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45049</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45616</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>46104</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45533</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45629</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45622</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>46107</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45114</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45986</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45946</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45302</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45615</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46114</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44805</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45822</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>44945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46125</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45160</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45995</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>44525</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45260</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45062</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>46132</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>44600</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45833</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45299</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45838</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45187</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45838</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45836</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45751</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45524</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45322</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45803</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45203</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45877</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45560</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45308</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45729</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44503</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44876</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45799</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>44607</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44634</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44519</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44589</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45824</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45196</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45243</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44664</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45260</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45201</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45299</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45880</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45149</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>44896</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45904</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45877</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46066</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46091</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45700</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45623</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45715</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45141</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45796</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45688</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45520</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45520</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45729</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45734</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45020</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>46142</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45222</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>46146</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>46146</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46105</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45106</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>44686</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>45103</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>46154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45288</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46154</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45641</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44533</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45320</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45148</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45785</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44666</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45615</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45382</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45937</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45061</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44547</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45092</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45861</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44544</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45755</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45761</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44629</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44985</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45880</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45880</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>46170</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>46170</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>45111</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44913</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44672</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45217</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44573</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46175</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>46178</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>46181</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>46181</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46181</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45382</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45635</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45721</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45630</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>46190</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>46190</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>46190</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>44727</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45096</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45575</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44735</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44873</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46205</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45636</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45219</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44887</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45041</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>44594</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45581</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45767</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>45068</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>44518</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44578</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>46258</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45120</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44995</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46220</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>46220</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>46222</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46222</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>46222</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>46222</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>46222</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46222</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45154</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46220</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46220</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>46220</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46220</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44979</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45175</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44952</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>46029</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45546</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45252</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>44593</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>44945</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>44491</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45723</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45218</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>44595</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>46270</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46270</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44649</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45911</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46281</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45707</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45450</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45370</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45366</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>44566</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45099</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44846</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>44708</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>44986</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>45565</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45012</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45222</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>44530</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>44715</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45163</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45544</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>44902</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45184</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45618</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45260</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45204</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45601</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>45028</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45051</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>45390</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>45390</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45688</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45258</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44634</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45524</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46254</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45693</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>46296</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>46296</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>46254</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45308</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45629</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44896</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45641</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45107</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>45261</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45300</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44593</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45131</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45645</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>44893</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45118</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>44746</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45299</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>44818</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45386</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45306</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>45775</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45736</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45229</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45411</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45713</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45616</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45782</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45784</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45784</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45784</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45784</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45784</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45789</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45553</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45337</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>44834</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44606</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45266</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45481</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45335</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>44901</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45476</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>44733</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>44763</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>44596</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>44735</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45716</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45964</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>46036</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44858</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>44635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>46049</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45197</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45733</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45375</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45014</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45932</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>46195</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45463</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44648</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44882</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44808</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>44493</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45359</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45929</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>44581</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44984</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45366</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44805</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44592</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44698</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45068</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45068</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44493</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>46049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44578</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45247</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46037</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44491</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>44593</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44498</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44482</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44662</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44599</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44839</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44650</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44882</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44740</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44882</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44544</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44488</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44594</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44687</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44825</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44483</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>44544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44711</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44613</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44531</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44593</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44574</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44537</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44482</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44867</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>44754</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>44533</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>44533</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>44516</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>44483</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44652</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44547</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44488</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44550</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44788</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44882</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44873</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>44622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45390</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>44952</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44995</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45049</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>45095</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45281</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45203</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45160</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44855</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45761</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45366</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45382</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45177</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45370</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45243</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45382</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45386</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45229</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45629</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45715</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45408</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45387</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45141</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44952</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45260</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45260</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45260</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45393</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45665</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45118</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45184</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45520</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45450</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45817</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45704</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45299</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44846</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45751</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45222</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45187</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45020</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45112</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45386</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45641</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45581</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45098</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45107</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45734</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45544</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45635</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44595</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45767</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45877</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45253</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44985</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45432</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44525</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45300</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45565</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45457</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45582</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45582</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45306</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45782</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45617</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44503</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45784</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45411</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45784</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45784</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45553</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45551</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>44986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44589</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45616</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45629</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44552</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45466</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45789</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45120</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45092</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45925</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45379</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44649</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45729</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44887</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45356</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44812</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45320</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45621</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45642</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45630</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44672</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44566</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45600</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45044</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45217</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>44902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44727</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44634</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44686</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45936</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45071</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45672</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45371</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45371</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45175</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45201</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44594</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44818</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44607</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45238</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>44979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45937</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>45524</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45049</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45720</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45560</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44593</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>44634</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45405</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45095</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45810</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45723</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45002</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45630</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45944</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45944</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45068</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45945</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45813</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45813</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45616</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45005</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45148</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45623</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45819</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45822</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45376</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45698</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44888</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45618</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44664</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45834</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45012</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45838</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45112</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45838</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45096</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45688</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44985</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45093</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44715</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44735</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45061</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44999</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45646</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45322</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45041</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45288</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45629</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45972</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45971</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45713</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45635</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45560</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45736</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44754</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45174</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45320</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45299</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45110</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45978</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45755</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45707</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45258</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44888</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45302</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45980</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45679</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45785</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>44519</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45880</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45711</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45487</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45880</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45881</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45693</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45039</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>44518</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45775</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45698</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46099</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46099</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45070</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44566</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46100</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46100</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>45520</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45729</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45177</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44578</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46107</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44904</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45308</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46107</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45581</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>44876</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44852</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45261</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45175</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>46114</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45721</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45559</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44491</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45995</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45622</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44945</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>46002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44593</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>46003</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46003</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45572</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45583</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44937</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45908</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44654</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>46009</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44484</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45803</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45824</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>46009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>44895</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44533</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45877</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45904</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46020</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>46010</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45688</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>44746</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44896</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45051</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45751</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45307</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45260</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45187</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45187</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46030</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45799</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45796</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44913</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45798</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45520</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45149</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45474</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>46031</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45154</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46034</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44573</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45880</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>46066</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>46091</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44530</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44708</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44893</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>44547</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45641</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45243</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45201</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45099</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45288</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45299</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45700</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45131</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45877</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45836</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>46049</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45524</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>46051</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>46142</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>46105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46146</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>46066</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>46146</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46066</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46069</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46154</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46082</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46086</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45978</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>46092</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46092</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>46094</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45861</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>46170</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>46170</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>46174</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46178</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46181</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>46178</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>46181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>46190</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>46190</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46190</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46203</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46205</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46204</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46222</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>46222</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>46222</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>46220</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46220</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46220</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46220</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>46220</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46222</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46222</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>46220</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46222</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>46029</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>46270</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>46270</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45911</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>46281</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46296</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>46254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46258</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46258</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>44606</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44733</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44596</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>44735</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45266</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45337</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>44834</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45481</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45335</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>44901</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45476</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>44763</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45716</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45964</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>46036</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44858</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>44635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>46049</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>45197</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45733</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45375</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45014</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45932</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>46195</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45463</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44648</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44882</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44808</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>44493</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45359</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45929</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>44581</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44984</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45366</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44805</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44592</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44949</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44686</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44698</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45068</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45068</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44493</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>46049</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44578</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45247</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>46037</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44491</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44804</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>44593</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44483</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44498</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44482</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44662</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>44566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44599</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44839</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44650</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44853</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44882</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44740</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44882</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44544</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44488</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>44594</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44687</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44825</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44483</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>44544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44711</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44613</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44531</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44593</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44574</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44537</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44482</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>44867</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>44754</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>44533</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>44533</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>44516</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>44483</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44652</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44547</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44488</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44550</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44788</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44882</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44873</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>44622</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45390</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>44952</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45035</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44995</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45049</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>45095</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45281</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45203</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45160</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44855</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45761</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45617</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45366</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45382</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45177</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45370</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45243</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45382</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45386</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45229</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45629</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45715</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45408</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45387</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45141</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45390</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44952</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45258</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45260</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45260</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45260</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45393</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45665</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45118</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45184</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45520</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45450</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45817</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45704</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45299</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44846</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45751</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45222</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45187</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45020</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45112</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45386</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45641</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45581</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45098</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45107</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45734</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45544</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45635</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>44595</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45767</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45877</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45253</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44985</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45432</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44525</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45300</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45615</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45565</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45457</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45582</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45582</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45306</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45782</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45617</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44503</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45784</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45411</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45784</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45784</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45553</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45551</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>44986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44589</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45616</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45629</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44552</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45466</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45789</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45120</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45092</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45925</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45379</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44649</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45729</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44887</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45356</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44812</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45320</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45621</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45642</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45630</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44672</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44566</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45600</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45044</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45217</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>44902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44727</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44634</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44686</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45936</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45071</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45672</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45936</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45371</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45371</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45175</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45201</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44594</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44818</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44607</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45238</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>44979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45937</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>45524</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45049</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45720</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45560</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44593</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>44634</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45405</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>45095</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45810</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45723</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45002</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45630</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45944</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45944</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45068</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45945</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45813</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45813</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45616</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45005</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45148</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45623</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45819</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45822</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45376</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45260</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45698</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44888</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45618</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44664</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45834</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45012</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45838</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45112</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45838</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45096</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45688</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44985</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45093</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44715</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44735</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45061</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>44999</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45646</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45322</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45041</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45288</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45629</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45972</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45971</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45713</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45635</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45560</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45736</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44754</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45174</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45320</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45163</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45299</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45110</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45978</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45755</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45707</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45258</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44888</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45302</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45980</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45679</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45785</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>44519</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45880</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45711</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45487</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45880</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45881</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45693</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45039</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>44518</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45775</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45698</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46099</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46099</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45070</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44566</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46100</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46100</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44544</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>45520</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45729</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45177</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44578</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45986</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46107</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44904</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45308</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46107</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45581</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>44876</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44852</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45261</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45175</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>46114</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45721</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45559</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>44491</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45995</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45622</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44945</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>46002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44593</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>46003</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46003</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45572</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45583</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>44937</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45908</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44654</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>46009</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44484</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45803</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45824</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>46009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>44895</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44533</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45877</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>45904</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46020</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>46010</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45688</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>44746</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44896</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45051</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45751</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45307</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45260</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45187</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45187</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46030</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45799</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45796</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>44913</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45798</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45520</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45149</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45474</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>46031</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45154</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46034</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45114</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44573</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45880</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>46066</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>46091</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44530</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44708</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44893</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>44547</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45641</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45243</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45201</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45099</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45288</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45299</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45700</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45131</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45877</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45836</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>46049</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45524</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>46051</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>46142</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>46105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46146</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>46066</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>46146</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46066</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46069</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46154</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46082</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46154</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46086</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45978</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45937</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>46092</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46092</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>46094</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45861</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>46170</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>46170</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>46174</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46178</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>46181</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>46178</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>46181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>46190</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>46190</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46190</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46203</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46205</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46204</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46222</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>46222</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>46222</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>46220</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46220</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46220</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46220</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>46220</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46222</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46222</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>46220</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46222</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>46029</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>46270</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>46270</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45911</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>46281</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46296</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>46254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46258</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46258</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>44606</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44733</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44596</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>44735</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45266</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45337</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>44834</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45266</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45481</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45335</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>44901</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45476</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>44763</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45716</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45964</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>46036</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44858</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45197</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>46163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>44635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46049</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45375</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45175</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45980</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>46195</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44808</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44493</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45929</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44493</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45359</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44592</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>44949</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44959</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45366</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>44650</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45974</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45713</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46093</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44493</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45035</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45068</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44698</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44984</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44686</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45607</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>46037</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44804</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44599</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>44593</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44498</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44650</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44594</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44687</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44656</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44712</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44711</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44537</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44701</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44652</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44550</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44613</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44574</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44593</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44754</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44547</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44788</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44872</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44622</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45039</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45393</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45387</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45095</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45307</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45201</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45071</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45698</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45260</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45487</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45583</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45077</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45110</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45093</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45281</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45376</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45238</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44902</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45320</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45457</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45177</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45371</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45371</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>45679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44895</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45704</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45168</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44754</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45112</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45698</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45095</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44566</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45559</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44654</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>44888</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45408</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45432</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44855</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44952</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45411</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45386</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45005</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44852</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44896</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45582</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45665</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45635</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45260</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>44984</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45520</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45629</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45114</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45751</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45877</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45302</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45308</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44805</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45799</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>44945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45824</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45792</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45798</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45260</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45880</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45817</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44896</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45187</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45904</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45877</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>46066</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44600</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>46091</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45700</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45688</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45299</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45877</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44816</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45911</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45322</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>46142</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45917</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46146</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46146</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45925</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44503</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44876</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44607</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>44634</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44519</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45936</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45243</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45201</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45299</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45149</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45623</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46154</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45715</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>46154</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45141</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45141</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45098</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45520</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45261</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45729</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45734</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45937</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45099</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45971</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45020</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45972</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45861</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45978</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45978</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45106</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44686</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45946</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45641</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44533</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45320</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44666</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45615</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45175</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45382</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45995</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45061</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>44547</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45092</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45600</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46170</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44544</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45755</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46003</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>46003</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45761</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44629</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>46002</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44985</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45111</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>44913</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>44672</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>46009</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45217</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>46009</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44573</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>46020</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46010</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45617</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46030</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46031</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45382</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45635</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46178</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45721</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45630</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45279</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46049</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45646</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44727</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46049</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46051</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46181</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45096</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45575</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>44735</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46069</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46066</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45219</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45273</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>44887</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45041</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44594</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45474</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>46190</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>46082</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45767</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>46086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>46190</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>46190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45068</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>46190</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46092</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46094</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>46094</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44578</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46100</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>46099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45581</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45120</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46099</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>46100</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46104</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46107</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45154</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45288</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46114</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44979</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45175</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>44952</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45546</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45252</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46125</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44945</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44491</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45035</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45723</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46203</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46132</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45260</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45218</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44595</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45908</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44649</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45636</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45630</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45707</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>45187</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45836</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45751</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45803</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45450</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45370</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45258</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45366</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44566</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45099</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44708</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>46220</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>46220</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46222</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>46222</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>46222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46222</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>46222</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>46222</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>44986</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45565</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>46220</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46220</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>46220</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45012</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>46029</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45222</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>44530</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45163</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44715</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45163</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>46272</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45544</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46270</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46270</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44902</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45184</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45618</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>45260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45911</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45070</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44999</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45204</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45049</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>46281</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45601</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45028</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>45051</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45390</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45390</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45688</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45258</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44634</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45524</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45693</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45308</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45629</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>44896</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45641</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45261</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45300</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44593</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45131</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45258</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45645</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44893</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45118</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44746</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45299</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44818</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45386</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45306</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45775</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45177</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45736</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45229</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45411</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46296</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45713</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45379</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46296</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46254</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45616</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46258</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45782</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45782</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45784</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45784</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45784</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45784</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45784</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45789</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45553</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45466</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45356</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44812</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45621</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>45642</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45044</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45630</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45800</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>44888</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45405</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45810</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45002</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45720</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45560</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45813</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45813</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45813</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45813</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45616</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45819</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45533</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45822</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45833</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45834</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45838</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45838</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45560</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45785</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45880</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45881</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45880</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45266</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45337</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44834</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>44606</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45266</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45481</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45335</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44901</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45476</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44733</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>44763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45076</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>44596</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>44735</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45716</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45964</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>45583</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>44858</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45197</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>46163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>44635</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46049</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46190</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45375</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45175</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45980</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45014</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>46195</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44808</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>44493</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45929</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44493</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45359</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44592</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>44949</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44959</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45366</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>44650</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45974</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45713</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46049</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46093</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44493</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45035</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45068</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>44698</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44984</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44686</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45607</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>46037</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44804</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44599</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>44593</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44498</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44650</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44498</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44594</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44687</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44656</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44712</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44711</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44537</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44701</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44652</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44550</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44613</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44574</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44593</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44754</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44547</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44788</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44872</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44622</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45039</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45393</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45387</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45095</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45307</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45201</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45071</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45698</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45260</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45487</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45583</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45077</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45110</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45093</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45281</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45376</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45238</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44902</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45320</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45457</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45177</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45371</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>45371</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>45679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44895</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45704</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45168</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44754</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45112</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45698</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45095</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44566</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45559</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44654</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>44888</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45408</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45432</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44855</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44952</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45411</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45386</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45005</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44852</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44896</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45582</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45665</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45635</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45260</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>44984</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45520</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45629</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45114</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45751</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45877</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45302</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45308</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44805</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45799</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>44945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45824</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45792</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45798</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45260</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45880</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45817</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44896</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45187</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45904</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45877</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>46066</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44600</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>46091</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45700</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45688</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45299</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45877</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44816</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45911</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45322</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>46142</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45917</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46146</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46146</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45925</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44503</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44876</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44607</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>44634</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44519</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45936</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45243</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45201</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45299</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45149</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45944</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>44938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45623</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46154</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45715</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>46154</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45141</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45141</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45098</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45520</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45261</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>45729</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45734</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45937</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45099</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45971</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45020</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45972</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45222</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45861</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45978</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45978</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45106</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44686</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45986</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45946</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45641</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44533</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45320</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44666</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45615</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45175</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45382</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45995</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45061</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>44547</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45092</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45600</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46170</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44544</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45755</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46003</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>46003</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45761</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44629</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>46002</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44985</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45111</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>44913</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>44672</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>46009</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45217</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>46009</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44573</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>46020</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46010</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45617</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46030</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46031</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45382</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45635</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46178</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45721</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45630</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45279</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>46049</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45646</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>46181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>44727</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46049</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>46051</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>46181</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45096</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45575</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>44735</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46069</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46066</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>44873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45219</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45273</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>44887</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45041</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44594</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45474</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>46190</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>46082</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45767</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>46086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>46190</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>46190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45068</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>46190</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>46092</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>46094</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>46094</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44578</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46100</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>46099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45581</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45120</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46099</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>46100</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46104</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46107</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45154</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45288</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46114</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44979</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45175</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>44952</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45546</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45252</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46125</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44945</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44491</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45035</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45723</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46203</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46132</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45260</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45218</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44595</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45908</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44649</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45636</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45630</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45707</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>45187</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45836</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45751</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45803</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45450</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45370</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45258</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45366</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>44566</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45099</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44708</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>46220</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>46220</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>46222</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>46222</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>46222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46222</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>46222</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>46222</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>44986</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45565</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>46220</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46220</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>46220</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45012</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>46029</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45222</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>44530</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45163</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44715</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45163</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>46272</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45544</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46270</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46270</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44902</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45184</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45618</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>45260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45911</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45070</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44999</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45204</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45049</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>46281</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45601</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45028</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>45051</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45390</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45390</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45688</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45258</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44634</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45524</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45693</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45308</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45629</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>44896</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45641</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45261</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45300</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44593</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45131</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45258</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45645</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44893</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45118</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44746</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45299</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44818</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45386</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45306</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45775</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45177</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45736</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45229</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45411</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46296</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45713</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45379</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46296</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46254</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45616</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46258</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45782</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45782</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45784</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45784</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45784</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45784</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45784</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>46258</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45789</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45553</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45466</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45356</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44812</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45621</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>45642</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45044</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45630</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45800</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>44888</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45405</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45810</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45002</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45720</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45560</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45813</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45813</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45813</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45813</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45616</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45819</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45533</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45822</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45833</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45834</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45838</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45838</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45560</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45785</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45880</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45881</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45880</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45266</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45337</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44834</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>44606</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>45266</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45481</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45335</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44901</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45476</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44733</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>44763</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45076</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>44596</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>44735</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45716</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45964</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>44838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44858</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45583</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46049</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45980</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45375</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45014</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44808</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44493</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45359</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45428</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45713</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45035</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44984</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44805</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45974</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44592</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46049</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45607</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46093</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44686</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45366</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44949</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44650</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44698</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45068</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44493</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46037</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44804</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44599</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44799</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44593</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44662</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44566</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44599</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>44839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>44498</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44740</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44687</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44656</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44711</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44501</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44533</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44825</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44593</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>44531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44547</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44788</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45572</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45062</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44872</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45817</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45583</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44882</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45792</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>44763</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45751</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45203</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45370</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44654</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44895</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44533</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44746</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45877</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45307</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45260</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44913</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45520</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45154</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45861</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45114</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44573</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44530</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44708</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44893</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44547</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45641</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45243</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45201</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45546</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45099</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45131</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45937</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45035</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46174</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45944</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45944</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45382</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45386</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45229</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45408</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45387</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45390</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>46181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44945</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44995</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>46181</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>46181</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>46181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45617</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45366</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45103</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45196</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45629</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45141</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45141</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45260</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46190</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45411</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45260</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45665</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45972</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45184</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45636</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46203</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45704</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45106</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45222</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46204</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45187</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45986</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45946</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45386</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45641</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45581</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45107</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45734</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45645</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45995</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45767</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45432</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45520</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45450</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45300</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>46222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46222</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>46222</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46220</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46220</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>46220</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>46220</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>46220</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46222</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>46220</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46002</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>46003</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46003</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45782</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45784</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45784</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45784</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45784</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45784</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45911</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45553</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46009</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46020</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45466</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>46281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45789</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>46030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45356</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44973</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45621</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45642</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45630</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45044</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46049</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45800</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>46049</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>46051</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45720</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45560</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45405</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45810</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45002</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45813</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45813</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46066</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45813</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45813</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>46066</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45616</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45533</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45299</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45819</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45822</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>46296</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46082</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46296</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46254</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45833</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45834</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45838</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45838</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>46092</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46092</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46094</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46099</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46099</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>46254</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46100</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>46100</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46104</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>46258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46107</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>46107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>46258</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>46114</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46125</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45635</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45785</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44595</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45880</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>46132</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45880</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45881</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46132</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>44896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45582</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>45582</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>44937</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45803</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45824</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45877</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45904</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45688</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44896</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45751</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46314</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>46314</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>44552</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45187</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45187</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45799</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45796</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>46270</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45798</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45120</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>46314</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45379</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>46270</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45880</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>46066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>44887</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46091</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>46272</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>45320</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45308</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45700</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>44629</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46316</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45877</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46318</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45836</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46318</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44672</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44902</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44634</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46142</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45071</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46105</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>46146</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44979</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45524</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45049</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45095</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45723</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45630</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44666</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45273</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45978</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45005</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45623</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45618</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45112</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45096</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44985</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45601</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45061</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44999</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45041</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45635</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45615</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45736</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45110</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45707</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45679</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>44519</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45711</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45039</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44518</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45698</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45070</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>44566</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45729</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>44578</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44852</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45721</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44873</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45028</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45095</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>44896</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44855</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45761</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45382</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45715</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44952</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45093</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45260</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45393</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45118</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44902</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45020</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45112</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45544</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44985</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44525</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45615</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45565</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45457</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>44959</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45306</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45617</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>44503</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>45411</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44986</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44589</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45616</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45629</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44649</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45729</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45630</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44566</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45600</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45217</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44727</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>44686</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45672</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>45371</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45371</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45201</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>44594</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>44818</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>44607</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45077</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44600</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>44593</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>44634</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45222</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45111</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45148</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45376</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45099</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45698</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44888</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45261</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>44664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45175</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45688</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44715</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44735</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45322</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45252</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45713</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44754</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45320</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45163</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45299</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45755</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45258</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45219</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44938</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44888</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45302</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44994</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45487</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45693</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>44544</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45520</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>44904</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45308</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45261</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45175</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45622</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>44945</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>44593</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44606</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44733</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>44596</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>44735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45266</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45337</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>44834</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45266</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45481</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45335</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>44901</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45476</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44763</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45076</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45716</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45964</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46036</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>

--- a/Översikt KARLSTAD.xlsx
+++ b/Översikt KARLSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44708</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>44715</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>44531</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45607</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>44838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44858</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45583</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46049</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>45197</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45980</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45375</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45932</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>45014</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44648</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44882</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44808</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44876</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44493</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>45929</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45359</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>46069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44493</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45428</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45713</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45035</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44984</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44805</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45974</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45974</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44592</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46049</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45607</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45838</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46093</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44686</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45068</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45366</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44949</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44650</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44698</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45068</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44493</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45247</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46037</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44804</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44599</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44799</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44593</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44536</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44662</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44566</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44599</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>44839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44650</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>44498</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44740</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44687</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44656</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44712</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44711</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44501</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44533</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44652</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44825</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44593</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>44531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44547</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44788</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45572</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45062</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44872</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45817</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45583</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44882</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45792</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>44763</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45751</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45203</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45370</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44654</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44895</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44533</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44746</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45877</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45307</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45260</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44913</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45520</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45154</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45861</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45114</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44573</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44530</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44708</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44893</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44547</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45641</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45243</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45201</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45546</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45099</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45131</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45937</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45035</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46174</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45944</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44816</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45944</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45382</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45386</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45229</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45408</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45387</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45390</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>46181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44945</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44995</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>46181</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>46181</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>46181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45617</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45366</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45103</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45196</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45629</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45141</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45141</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45260</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46190</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46190</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45411</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45260</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45665</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>44805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45972</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45184</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45636</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46203</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45704</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45106</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45222</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46204</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45187</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45986</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45946</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45386</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45641</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45581</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45107</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45734</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45645</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45995</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45767</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45253</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45432</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45520</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45450</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45300</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>46222</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46222</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>46222</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46220</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46220</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>46220</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>46220</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>46220</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46222</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>46220</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46002</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>46003</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46003</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45782</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45784</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45784</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45784</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45784</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45784</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45911</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45553</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46009</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46020</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45466</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>46281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45789</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>46030</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46031</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45356</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44812</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44973</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45621</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45642</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45630</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45044</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46049</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45800</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>46049</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>46051</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45720</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45560</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45405</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45810</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45002</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44888</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45813</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45813</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46066</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45813</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45813</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>46066</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45616</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45533</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45299</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45819</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45822</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>46296</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46082</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46296</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46254</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45833</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45834</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45838</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45838</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>46092</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46092</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46094</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46099</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46099</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>46254</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46100</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>46100</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46104</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>46258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46107</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>46107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>46258</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>46114</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46125</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45635</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45785</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44595</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45880</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>46132</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45880</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45881</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46132</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>44896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45582</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>45582</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>44937</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45803</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45824</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45877</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45904</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45688</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44896</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45751</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46314</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>46314</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>44552</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45187</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45187</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45799</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45796</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>46270</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45798</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45120</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>46314</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45379</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>46270</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45880</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>46066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>44887</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46091</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>46272</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>45320</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45308</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45700</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>44629</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46316</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45877</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46318</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45836</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46318</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44672</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44902</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44634</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>46142</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45071</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46105</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>46146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>46146</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44979</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45524</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45049</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45095</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45723</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45630</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44666</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45273</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45978</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45005</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45623</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45618</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45112</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45096</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44985</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45601</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45061</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44999</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45041</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45635</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45615</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45736</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45110</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45707</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45679</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>44519</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45711</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45039</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44518</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45698</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45070</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>44566</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45729</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>44578</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44852</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45721</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44873</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45028</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45095</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>44896</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44855</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45761</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45382</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45715</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44952</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45093</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45260</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45393</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45118</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44902</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45020</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45112</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45544</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>44985</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44525</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45615</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45565</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45457</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>44959</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45306</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45617</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>44503</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>45411</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44986</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>44589</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45616</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45629</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44649</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45729</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45630</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>44566</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45600</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45217</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44727</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>44686</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45672</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>45371</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45371</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>45175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45201</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>44594</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>44818</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>44607</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45077</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44600</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>44593</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>44634</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45222</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45111</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45148</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45376</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45099</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45698</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44888</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45261</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>44664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45175</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45688</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44715</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44735</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45322</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45252</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45713</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>44754</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45320</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45163</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45299</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45755</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45258</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45219</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44938</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44888</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45302</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44994</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45487</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>45693</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>44544</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45520</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>44904</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45308</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45261</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45175</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45559</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45622</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>44945</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>44593</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44606</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44733</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>44596</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>44735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45266</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45337</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>44834</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45266</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45481</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45335</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>44901</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45476</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44763</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45076</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45716</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45964</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46036</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
